--- a/rtss-pre1917/src/main/resources/Poland-1881-1893.xlsx
+++ b/rtss-pre1917/src/main/resources/Poland-1881-1893.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{381827AF-4C91-42A0-BB54-B5DA83D5CC18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49DBE482-92D7-4827-9AE1-C45E6408BCE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57690" yWindow="0" windowWidth="24420" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="notes" sheetId="2" r:id="rId1"/>
@@ -58,15 +58,6 @@
   </si>
   <si>
     <t>чр-о</t>
-  </si>
-  <si>
-    <t>чу-м</t>
-  </si>
-  <si>
-    <t>чу-ж</t>
-  </si>
-  <si>
-    <t>чу-о</t>
   </si>
   <si>
     <t>чеп</t>
@@ -213,9 +204,6 @@
     <t>vd-чр</t>
   </si>
   <si>
-    <t>vd-чу</t>
-  </si>
-  <si>
     <t>vd-чеп</t>
   </si>
   <si>
@@ -235,6 +223,18 @@
   </si>
   <si>
     <t>Все 9 двухстраничных разворотов: печатные стр. 146-163</t>
+  </si>
+  <si>
+    <t>vd-чc</t>
+  </si>
+  <si>
+    <t>чс-м</t>
+  </si>
+  <si>
+    <t>чс-ж</t>
+  </si>
+  <si>
+    <t>чс-о</t>
   </si>
 </sst>
 </file>
@@ -429,7 +429,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -526,13 +526,6 @@
     <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="2" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -768,178 +761,178 @@
       <c r="B1" s="2"/>
     </row>
     <row r="2" spans="1:3" ht="12.85" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="44"/>
+    </row>
+    <row r="3" spans="1:3" ht="12.85" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="46" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="48" t="s">
+      <c r="C3" s="44"/>
+    </row>
+    <row r="4" spans="1:3" ht="12.85" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="46" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="49"/>
-    </row>
-    <row r="3" spans="1:3" ht="12.85" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="51" t="s">
+      <c r="B4" s="43" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" s="44"/>
+    </row>
+    <row r="5" spans="1:3" ht="12.85" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="48" t="s">
+      <c r="B5" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="49"/>
-    </row>
-    <row r="4" spans="1:3" ht="12.85" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="51" t="s">
+      <c r="C5" s="44"/>
+    </row>
+    <row r="6" spans="1:3" ht="12.85" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="46"/>
+      <c r="B6" s="43"/>
+      <c r="C6" s="44"/>
+    </row>
+    <row r="7" spans="1:3" ht="12.85" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="48" t="s">
-        <v>66</v>
-      </c>
-      <c r="C4" s="49"/>
-    </row>
-    <row r="5" spans="1:3" ht="12.85" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="51" t="s">
+      <c r="B7" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="48" t="s">
+      <c r="C7" s="44"/>
+    </row>
+    <row r="8" spans="1:3" ht="12.85" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="46" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="49"/>
-    </row>
-    <row r="6" spans="1:3" ht="12.85" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="51"/>
-      <c r="B6" s="48"/>
-      <c r="C6" s="49"/>
-    </row>
-    <row r="7" spans="1:3" ht="12.85" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="51" t="s">
+      <c r="B8" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="48" t="s">
+      <c r="C8" s="44"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="49"/>
-    </row>
-    <row r="8" spans="1:3" ht="12.85" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="51" t="s">
+      <c r="B9" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="B8" s="48" t="s">
+      <c r="C9" s="44"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="46" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="49"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="51" t="s">
+      <c r="B10" s="45" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="50" t="s">
+      <c r="C10" s="44"/>
+    </row>
+    <row r="11" spans="1:3" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="46" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="49"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="51" t="s">
+      <c r="B11" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="50" t="s">
+      <c r="C11" s="44"/>
+    </row>
+    <row r="12" spans="1:3" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="46" t="s">
         <v>41</v>
       </c>
-      <c r="C10" s="49"/>
-    </row>
-    <row r="11" spans="1:3" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="51" t="s">
+      <c r="B12" s="45" t="s">
         <v>42</v>
       </c>
-      <c r="B11" s="50" t="s">
+      <c r="C12" s="44"/>
+    </row>
+    <row r="13" spans="1:3" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="46" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="49"/>
-    </row>
-    <row r="12" spans="1:3" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="51" t="s">
+      <c r="B13" s="45" t="s">
         <v>44</v>
       </c>
-      <c r="B12" s="50" t="s">
+      <c r="C13" s="44"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="46" t="s">
         <v>45</v>
       </c>
-      <c r="C12" s="49"/>
-    </row>
-    <row r="13" spans="1:3" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="51" t="s">
+      <c r="B14" s="45" t="s">
         <v>46</v>
       </c>
-      <c r="B13" s="50" t="s">
+      <c r="C14" s="44"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="C13" s="49"/>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="51" t="s">
+      <c r="B15" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="B14" s="50" t="s">
+      <c r="C15" s="44"/>
+    </row>
+    <row r="16" spans="1:3" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="46" t="s">
         <v>49</v>
       </c>
-      <c r="C14" s="49"/>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="51" t="s">
+      <c r="B16" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="B15" s="50" t="s">
+      <c r="C16" s="44"/>
+    </row>
+    <row r="17" spans="1:3" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="C15" s="49"/>
-    </row>
-    <row r="16" spans="1:3" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="51" t="s">
+      <c r="B17" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="B16" s="50" t="s">
-        <v>53</v>
-      </c>
-      <c r="C16" s="49"/>
-    </row>
-    <row r="17" spans="1:3" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="51" t="s">
-        <v>54</v>
-      </c>
-      <c r="B17" s="50" t="s">
-        <v>55</v>
-      </c>
-      <c r="C17" s="49"/>
+      <c r="C17" s="44"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="49"/>
-      <c r="B18" s="49"/>
-      <c r="C18" s="49"/>
+      <c r="A18" s="44"/>
+      <c r="B18" s="44"/>
+      <c r="C18" s="44"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="49"/>
-      <c r="B19" s="49"/>
-      <c r="C19" s="49"/>
+      <c r="A19" s="44"/>
+      <c r="B19" s="44"/>
+      <c r="C19" s="44"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="49" t="s">
-        <v>64</v>
-      </c>
-      <c r="B20" s="49"/>
-      <c r="C20" s="49"/>
+      <c r="A20" s="44" t="s">
+        <v>60</v>
+      </c>
+      <c r="B20" s="44"/>
+      <c r="C20" s="44"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="49" t="s">
-        <v>65</v>
-      </c>
-      <c r="B21" s="49"/>
-      <c r="C21" s="49"/>
+      <c r="A21" s="44" t="s">
+        <v>61</v>
+      </c>
+      <c r="B21" s="44"/>
+      <c r="C21" s="44"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="49"/>
-      <c r="B22" s="49"/>
-      <c r="C22" s="49"/>
+      <c r="A22" s="44"/>
+      <c r="B22" s="44"/>
+      <c r="C22" s="44"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="49"/>
-      <c r="B23" s="49"/>
-      <c r="C23" s="49"/>
+      <c r="A23" s="44"/>
+      <c r="B23" s="44"/>
+      <c r="C23" s="44"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -984,51 +977,51 @@
         <v>7</v>
       </c>
       <c r="I1" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="L1" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="M1" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="N1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="11" t="s">
+      <c r="O1" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="13" t="s">
-        <v>14</v>
-      </c>
       <c r="Q1" s="41" t="s">
+        <v>54</v>
+      </c>
+      <c r="R1" s="41" t="s">
+        <v>55</v>
+      </c>
+      <c r="S1" s="41" t="s">
+        <v>63</v>
+      </c>
+      <c r="T1" s="41" t="s">
+        <v>56</v>
+      </c>
+      <c r="U1" s="41" t="s">
+        <v>59</v>
+      </c>
+      <c r="V1" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="W1" s="41" t="s">
         <v>57</v>
-      </c>
-      <c r="R1" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="S1" s="41" t="s">
-        <v>59</v>
-      </c>
-      <c r="T1" s="41" t="s">
-        <v>60</v>
-      </c>
-      <c r="U1" s="41" t="s">
-        <v>63</v>
-      </c>
-      <c r="V1" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="W1" s="41" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="14" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B2" s="15">
         <v>1881</v>
@@ -1103,7 +1096,7 @@
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="19" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B3" s="20">
         <v>1882</v>
@@ -1178,7 +1171,7 @@
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="14" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B4" s="15">
         <v>1883</v>
@@ -1253,7 +1246,7 @@
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="19" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B5" s="20">
         <v>1884</v>
@@ -1328,7 +1321,7 @@
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="14" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B6" s="15">
         <v>1885</v>
@@ -1403,7 +1396,7 @@
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="19" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B7" s="20">
         <v>1886</v>
@@ -1478,7 +1471,7 @@
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="14" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B8" s="15">
         <v>1887</v>
@@ -1553,7 +1546,7 @@
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="19" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B9" s="20">
         <v>1888</v>
@@ -1628,7 +1621,7 @@
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="14" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B10" s="15">
         <v>1889</v>
@@ -1703,7 +1696,7 @@
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="19" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B11" s="20">
         <v>1890</v>
@@ -1778,7 +1771,7 @@
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="14" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B12" s="15">
         <v>1891</v>
@@ -1853,7 +1846,7 @@
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="19" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B13" s="20">
         <v>1892</v>
@@ -1928,7 +1921,7 @@
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="14" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B14" s="15">
         <v>1893</v>
@@ -2003,7 +1996,7 @@
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="19" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B15" s="20">
         <v>1881</v>
@@ -2078,7 +2071,7 @@
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="14" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B16" s="15">
         <v>1882</v>
@@ -2153,7 +2146,7 @@
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="19" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B17" s="20">
         <v>1883</v>
@@ -2228,7 +2221,7 @@
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="14" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B18" s="15">
         <v>1884</v>
@@ -2303,7 +2296,7 @@
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="19" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B19" s="20">
         <v>1885</v>
@@ -2378,7 +2371,7 @@
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="14" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B20" s="15">
         <v>1886</v>
@@ -2453,7 +2446,7 @@
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="19" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B21" s="20">
         <v>1887</v>
@@ -2528,7 +2521,7 @@
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="14" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B22" s="15">
         <v>1888</v>
@@ -2603,7 +2596,7 @@
     </row>
     <row r="23" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="19" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B23" s="20">
         <v>1889</v>
@@ -2678,7 +2671,7 @@
     </row>
     <row r="24" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="14" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B24" s="15">
         <v>1890</v>
@@ -2753,7 +2746,7 @@
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="19" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B25" s="20">
         <v>1891</v>
@@ -2828,7 +2821,7 @@
     </row>
     <row r="26" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="14" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B26" s="15">
         <v>1892</v>
@@ -2903,7 +2896,7 @@
     </row>
     <row r="27" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="19" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B27" s="20">
         <v>1893</v>
@@ -2978,7 +2971,7 @@
     </row>
     <row r="28" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="14" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B28" s="15">
         <v>1881</v>
@@ -3053,7 +3046,7 @@
     </row>
     <row r="29" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="19" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B29" s="20">
         <v>1882</v>
@@ -3128,7 +3121,7 @@
     </row>
     <row r="30" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="14" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B30" s="15">
         <v>1883</v>
@@ -3203,7 +3196,7 @@
     </row>
     <row r="31" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="19" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B31" s="20">
         <v>1884</v>
@@ -3278,7 +3271,7 @@
     </row>
     <row r="32" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="14" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B32" s="15">
         <v>1885</v>
@@ -3353,7 +3346,7 @@
     </row>
     <row r="33" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="19" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B33" s="20">
         <v>1886</v>
@@ -3428,7 +3421,7 @@
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="14" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B34" s="15">
         <v>1887</v>
@@ -3503,7 +3496,7 @@
     </row>
     <row r="35" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="19" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B35" s="20">
         <v>1888</v>
@@ -3518,10 +3511,10 @@
         <v>837317</v>
       </c>
       <c r="F35" s="32" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G35" s="32" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="H35" s="21">
         <v>32320</v>
@@ -3575,7 +3568,7 @@
     </row>
     <row r="36" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="14" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B36" s="15">
         <v>1889</v>
@@ -3650,7 +3643,7 @@
     </row>
     <row r="37" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="19" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B37" s="20">
         <v>1890</v>
@@ -3725,7 +3718,7 @@
     </row>
     <row r="38" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="14" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B38" s="15">
         <v>1891</v>
@@ -3800,7 +3793,7 @@
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="19" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B39" s="20">
         <v>1892</v>
@@ -3875,7 +3868,7 @@
     </row>
     <row r="40" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="14" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B40" s="15">
         <v>1893</v>
@@ -3950,7 +3943,7 @@
     </row>
     <row r="41" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="19" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B41" s="20">
         <v>1881</v>
@@ -4025,7 +4018,7 @@
     </row>
     <row r="42" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B42" s="15">
         <v>1882</v>
@@ -4100,7 +4093,7 @@
     </row>
     <row r="43" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="19" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B43" s="20">
         <v>1883</v>
@@ -4175,7 +4168,7 @@
     </row>
     <row r="44" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B44" s="15">
         <v>1884</v>
@@ -4250,7 +4243,7 @@
     </row>
     <row r="45" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="19" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B45" s="20">
         <v>1885</v>
@@ -4325,7 +4318,7 @@
     </row>
     <row r="46" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B46" s="15">
         <v>1886</v>
@@ -4400,7 +4393,7 @@
     </row>
     <row r="47" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="19" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B47" s="20">
         <v>1887</v>
@@ -4475,7 +4468,7 @@
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B48" s="15">
         <v>1888</v>
@@ -4550,7 +4543,7 @@
     </row>
     <row r="49" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="19" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B49" s="20">
         <v>1889</v>
@@ -4625,7 +4618,7 @@
     </row>
     <row r="50" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B50" s="15">
         <v>1890</v>
@@ -4700,7 +4693,7 @@
     </row>
     <row r="51" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="19" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B51" s="20">
         <v>1891</v>
@@ -4775,7 +4768,7 @@
     </row>
     <row r="52" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B52" s="15">
         <v>1892</v>
@@ -4850,7 +4843,7 @@
     </row>
     <row r="53" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="19" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B53" s="20">
         <v>1893</v>
@@ -4925,16 +4918,16 @@
     </row>
     <row r="54" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="24" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B54" s="25">
         <v>1881</v>
       </c>
       <c r="C54" s="26" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D54" s="26" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E54" s="27">
         <v>543091</v>
@@ -4997,16 +4990,16 @@
     </row>
     <row r="55" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="30" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B55" s="31">
         <v>1882</v>
       </c>
       <c r="C55" s="32" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D55" s="32" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E55" s="33">
         <v>549982</v>
@@ -5069,16 +5062,16 @@
     </row>
     <row r="56" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="24" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B56" s="25">
         <v>1883</v>
       </c>
       <c r="C56" s="26" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D56" s="26" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E56" s="27">
         <v>552222</v>
@@ -5141,16 +5134,16 @@
     </row>
     <row r="57" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="30" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B57" s="31">
         <v>1884</v>
       </c>
       <c r="C57" s="32" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D57" s="32" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E57" s="33">
         <v>563586</v>
@@ -5213,16 +5206,16 @@
     </row>
     <row r="58" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="24" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B58" s="25">
         <v>1885</v>
       </c>
       <c r="C58" s="26" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D58" s="26" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E58" s="27">
         <v>575004</v>
@@ -5285,16 +5278,16 @@
     </row>
     <row r="59" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="30" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B59" s="31">
         <v>1886</v>
       </c>
       <c r="C59" s="32" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D59" s="32" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E59" s="33">
         <v>594129</v>
@@ -5357,16 +5350,16 @@
     </row>
     <row r="60" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="24" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B60" s="25">
         <v>1887</v>
       </c>
       <c r="C60" s="26" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D60" s="26" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E60" s="27">
         <v>601587</v>
@@ -5429,16 +5422,16 @@
     </row>
     <row r="61" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="30" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B61" s="31">
         <v>1888</v>
       </c>
       <c r="C61" s="32" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D61" s="32" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E61" s="33">
         <v>607819</v>
@@ -5501,16 +5494,16 @@
     </row>
     <row r="62" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="24" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B62" s="25">
         <v>1889</v>
       </c>
       <c r="C62" s="26" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D62" s="26" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E62" s="27">
         <v>593941</v>
@@ -5573,7 +5566,7 @@
     </row>
     <row r="63" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" s="30" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B63" s="31">
         <v>1890</v>
@@ -5648,7 +5641,7 @@
     </row>
     <row r="64" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="24" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B64" s="25">
         <v>1891</v>
@@ -5723,7 +5716,7 @@
     </row>
     <row r="65" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="30" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B65" s="31">
         <v>1892</v>
@@ -5798,7 +5791,7 @@
     </row>
     <row r="66" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="24" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B66" s="25">
         <v>1893</v>
@@ -5873,7 +5866,7 @@
     </row>
     <row r="67" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="30" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B67" s="31">
         <v>1881</v>
@@ -5948,7 +5941,7 @@
     </row>
     <row r="68" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" s="24" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B68" s="25">
         <v>1882</v>
@@ -6023,7 +6016,7 @@
     </row>
     <row r="69" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="30" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B69" s="31">
         <v>1883</v>
@@ -6098,7 +6091,7 @@
     </row>
     <row r="70" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="24" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B70" s="25">
         <v>1884</v>
@@ -6173,7 +6166,7 @@
     </row>
     <row r="71" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="30" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B71" s="31">
         <v>1885</v>
@@ -6248,16 +6241,16 @@
     </row>
     <row r="72" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="24" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B72" s="25">
         <v>1886</v>
       </c>
       <c r="C72" s="26" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D72" s="26" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E72" s="27">
         <v>925497</v>
@@ -6320,16 +6313,16 @@
     </row>
     <row r="73" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="30" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B73" s="31">
         <v>1887</v>
       </c>
       <c r="C73" s="32" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D73" s="32" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E73" s="33">
         <v>945238</v>
@@ -6392,16 +6385,16 @@
     </row>
     <row r="74" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="24" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B74" s="25">
         <v>1888</v>
       </c>
       <c r="C74" s="26" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D74" s="26" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E74" s="27">
         <v>979700</v>
@@ -6464,7 +6457,7 @@
     </row>
     <row r="75" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="30" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B75" s="31">
         <v>1889</v>
@@ -6539,7 +6532,7 @@
     </row>
     <row r="76" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="24" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B76" s="25">
         <v>1890</v>
@@ -6614,7 +6607,7 @@
     </row>
     <row r="77" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="30" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B77" s="31">
         <v>1891</v>
@@ -6689,7 +6682,7 @@
     </row>
     <row r="78" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="24" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B78" s="25">
         <v>1892</v>
@@ -6764,7 +6757,7 @@
     </row>
     <row r="79" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" s="30" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B79" s="31">
         <v>1893</v>
@@ -6839,7 +6832,7 @@
     </row>
     <row r="80" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" s="24" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B80" s="25">
         <v>1881</v>
@@ -6914,7 +6907,7 @@
     </row>
     <row r="81" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" s="30" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B81" s="31">
         <v>1882</v>
@@ -6989,7 +6982,7 @@
     </row>
     <row r="82" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" s="24" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B82" s="25">
         <v>1883</v>
@@ -7064,7 +7057,7 @@
     </row>
     <row r="83" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" s="30" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B83" s="31">
         <v>1884</v>
@@ -7139,7 +7132,7 @@
     </row>
     <row r="84" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" s="24" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B84" s="25">
         <v>1885</v>
@@ -7214,7 +7207,7 @@
     </row>
     <row r="85" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" s="30" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B85" s="31">
         <v>1886</v>
@@ -7289,7 +7282,7 @@
     </row>
     <row r="86" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" s="24" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B86" s="25">
         <v>1887</v>
@@ -7364,7 +7357,7 @@
     </row>
     <row r="87" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="30" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B87" s="31">
         <v>1888</v>
@@ -7439,7 +7432,7 @@
     </row>
     <row r="88" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="24" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B88" s="25">
         <v>1889</v>
@@ -7514,7 +7507,7 @@
     </row>
     <row r="89" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" s="30" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B89" s="31">
         <v>1890</v>
@@ -7589,7 +7582,7 @@
     </row>
     <row r="90" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" s="24" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B90" s="25">
         <v>1891</v>
@@ -7664,7 +7657,7 @@
     </row>
     <row r="91" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" s="30" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B91" s="31">
         <v>1892</v>
@@ -7739,7 +7732,7 @@
     </row>
     <row r="92" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" s="24" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B92" s="25">
         <v>1893</v>
@@ -7814,7 +7807,7 @@
     </row>
     <row r="93" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" s="30" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B93" s="31">
         <v>1881</v>
@@ -7889,7 +7882,7 @@
     </row>
     <row r="94" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" s="24" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B94" s="25">
         <v>1882</v>
@@ -7964,7 +7957,7 @@
     </row>
     <row r="95" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" s="30" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B95" s="31">
         <v>1883</v>
@@ -8039,7 +8032,7 @@
     </row>
     <row r="96" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" s="24" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B96" s="25">
         <v>1884</v>
@@ -8114,7 +8107,7 @@
     </row>
     <row r="97" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" s="30" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B97" s="31">
         <v>1885</v>
@@ -8189,7 +8182,7 @@
     </row>
     <row r="98" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" s="24" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B98" s="25">
         <v>1886</v>
@@ -8206,7 +8199,7 @@
       <c r="F98" s="27">
         <v>13240</v>
       </c>
-      <c r="G98" s="47">
+      <c r="G98" s="42">
         <v>12888</v>
       </c>
       <c r="H98" s="27">
@@ -8264,7 +8257,7 @@
     </row>
     <row r="99" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" s="30" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B99" s="31">
         <v>1887</v>
@@ -8339,7 +8332,7 @@
     </row>
     <row r="100" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" s="24" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B100" s="25">
         <v>1888</v>
@@ -8414,7 +8407,7 @@
     </row>
     <row r="101" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" s="30" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B101" s="31">
         <v>1889</v>
@@ -8489,7 +8482,7 @@
     </row>
     <row r="102" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" s="24" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B102" s="25">
         <v>1890</v>
@@ -8564,7 +8557,7 @@
     </row>
     <row r="103" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" s="30" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B103" s="31">
         <v>1891</v>
@@ -8639,7 +8632,7 @@
     </row>
     <row r="104" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" s="24" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B104" s="25">
         <v>1892</v>
@@ -8714,7 +8707,7 @@
     </row>
     <row r="105" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" s="30" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B105" s="31">
         <v>1893</v>
@@ -8789,7 +8782,7 @@
     </row>
     <row r="106" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A106" s="24" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B106" s="25">
         <v>1881</v>
@@ -8864,7 +8857,7 @@
     </row>
     <row r="107" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" s="30" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B107" s="31">
         <v>1882</v>
@@ -8939,7 +8932,7 @@
     </row>
     <row r="108" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" s="24" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B108" s="25">
         <v>1883</v>
@@ -9014,7 +9007,7 @@
     </row>
     <row r="109" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A109" s="30" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B109" s="31">
         <v>1884</v>
@@ -9089,7 +9082,7 @@
     </row>
     <row r="110" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A110" s="24" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B110" s="25">
         <v>1885</v>
@@ -9164,7 +9157,7 @@
     </row>
     <row r="111" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A111" s="30" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B111" s="31">
         <v>1886</v>
@@ -9239,7 +9232,7 @@
     </row>
     <row r="112" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A112" s="24" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B112" s="25">
         <v>1887</v>
@@ -9262,7 +9255,7 @@
       <c r="H112" s="27">
         <v>26725</v>
       </c>
-      <c r="I112" s="47">
+      <c r="I112" s="42">
         <v>8240</v>
       </c>
       <c r="J112" s="27">
@@ -9314,7 +9307,7 @@
     </row>
     <row r="113" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A113" s="30" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B113" s="31">
         <v>1888</v>
@@ -9389,7 +9382,7 @@
     </row>
     <row r="114" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A114" s="24" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B114" s="25">
         <v>1889</v>
@@ -9464,7 +9457,7 @@
     </row>
     <row r="115" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A115" s="30" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B115" s="31">
         <v>1890</v>
@@ -9539,7 +9532,7 @@
     </row>
     <row r="116" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A116" s="24" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B116" s="25">
         <v>1891</v>
@@ -9614,7 +9607,7 @@
     </row>
     <row r="117" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A117" s="30" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B117" s="31">
         <v>1892</v>
@@ -9689,7 +9682,7 @@
     </row>
     <row r="118" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A118" s="24" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B118" s="25">
         <v>1893</v>
@@ -9764,7 +9757,7 @@
     </row>
     <row r="119" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A119" s="30" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B119" s="31">
         <v>1881</v>
@@ -9839,7 +9832,7 @@
     </row>
     <row r="120" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A120" s="24" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B120" s="25">
         <v>1882</v>
@@ -9914,7 +9907,7 @@
     </row>
     <row r="121" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A121" s="30" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B121" s="31">
         <v>1883</v>
@@ -9989,7 +9982,7 @@
     </row>
     <row r="122" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A122" s="24" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B122" s="25">
         <v>1884</v>
@@ -10064,7 +10057,7 @@
     </row>
     <row r="123" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A123" s="30" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B123" s="31">
         <v>1885</v>
@@ -10139,7 +10132,7 @@
     </row>
     <row r="124" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A124" s="24" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B124" s="25">
         <v>1886</v>
@@ -10214,7 +10207,7 @@
     </row>
     <row r="125" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A125" s="30" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B125" s="31">
         <v>1887</v>
@@ -10289,7 +10282,7 @@
     </row>
     <row r="126" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A126" s="24" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B126" s="25">
         <v>1888</v>
@@ -10364,7 +10357,7 @@
     </row>
     <row r="127" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A127" s="30" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B127" s="31">
         <v>1889</v>
@@ -10439,7 +10432,7 @@
     </row>
     <row r="128" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A128" s="24" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B128" s="25">
         <v>1890</v>
@@ -10514,7 +10507,7 @@
     </row>
     <row r="129" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A129" s="30" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B129" s="31">
         <v>1891</v>
@@ -10589,7 +10582,7 @@
     </row>
     <row r="130" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A130" s="24" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B130" s="25">
         <v>1892</v>
@@ -10664,7 +10657,7 @@
     </row>
     <row r="131" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A131" s="30" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B131" s="31">
         <v>1893</v>
@@ -10739,16 +10732,16 @@
     </row>
     <row r="132" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A132" s="24" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B132" s="25">
         <v>1881</v>
       </c>
       <c r="C132" s="26" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D132" s="26" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E132" s="27">
         <v>613203</v>
@@ -10811,16 +10804,16 @@
     </row>
     <row r="133" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A133" s="30" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B133" s="31">
         <v>1882</v>
       </c>
       <c r="C133" s="32" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D133" s="32" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E133" s="33">
         <v>616649</v>
@@ -10883,16 +10876,16 @@
     </row>
     <row r="134" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A134" s="24" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B134" s="25">
         <v>1883</v>
       </c>
       <c r="C134" s="26" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D134" s="26" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E134" s="27">
         <v>622465</v>
@@ -10955,7 +10948,7 @@
     </row>
     <row r="135" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A135" s="30" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B135" s="31">
         <v>1884</v>
@@ -11030,7 +11023,7 @@
     </row>
     <row r="136" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A136" s="24" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B136" s="25">
         <v>1885</v>
@@ -11105,7 +11098,7 @@
     </row>
     <row r="137" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A137" s="30" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B137" s="31">
         <v>1886</v>
@@ -11180,7 +11173,7 @@
     </row>
     <row r="138" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A138" s="24" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B138" s="25">
         <v>1887</v>
@@ -11255,7 +11248,7 @@
     </row>
     <row r="139" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A139" s="30" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B139" s="31">
         <v>1888</v>
@@ -11330,7 +11323,7 @@
     </row>
     <row r="140" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A140" s="24" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B140" s="25">
         <v>1889</v>
@@ -11405,7 +11398,7 @@
     </row>
     <row r="141" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A141" s="30" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B141" s="31">
         <v>1890</v>
@@ -11480,7 +11473,7 @@
     </row>
     <row r="142" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A142" s="24" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B142" s="25">
         <v>1891</v>
@@ -11555,7 +11548,7 @@
     </row>
     <row r="143" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A143" s="30" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B143" s="31">
         <v>1892</v>
@@ -11630,7 +11623,7 @@
     </row>
     <row r="144" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A144" s="24" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B144" s="25">
         <v>1893</v>
@@ -11704,21 +11697,21 @@
       </c>
     </row>
     <row r="145" spans="1:23" x14ac:dyDescent="0.55000000000000004">
-      <c r="A145" s="42"/>
-      <c r="B145" s="43"/>
-      <c r="C145" s="44"/>
-      <c r="D145" s="44"/>
-      <c r="E145" s="44"/>
-      <c r="F145" s="44"/>
-      <c r="G145" s="44"/>
-      <c r="H145" s="44"/>
-      <c r="I145" s="44"/>
-      <c r="J145" s="44"/>
-      <c r="K145" s="44"/>
-      <c r="L145" s="44"/>
-      <c r="M145" s="45"/>
-      <c r="N145" s="45"/>
-      <c r="O145" s="46"/>
+      <c r="A145" s="30"/>
+      <c r="B145" s="31"/>
+      <c r="C145" s="33"/>
+      <c r="D145" s="33"/>
+      <c r="E145" s="33"/>
+      <c r="F145" s="33"/>
+      <c r="G145" s="33"/>
+      <c r="H145" s="33"/>
+      <c r="I145" s="33"/>
+      <c r="J145" s="33"/>
+      <c r="K145" s="33"/>
+      <c r="L145" s="33"/>
+      <c r="M145" s="34"/>
+      <c r="N145" s="34"/>
+      <c r="O145" s="35"/>
       <c r="Q145" s="4"/>
       <c r="R145" s="4"/>
       <c r="S145" s="4"/>
@@ -11729,7 +11722,7 @@
     </row>
     <row r="146" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A146" s="30" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B146" s="31">
         <v>1881</v>
@@ -11804,7 +11797,7 @@
     </row>
     <row r="147" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A147" s="24" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B147" s="25">
         <v>1882</v>
@@ -11879,7 +11872,7 @@
     </row>
     <row r="148" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A148" s="30" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B148" s="31">
         <v>1883</v>
@@ -11954,7 +11947,7 @@
     </row>
     <row r="149" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A149" s="24" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B149" s="25">
         <v>1884</v>
@@ -12029,7 +12022,7 @@
     </row>
     <row r="150" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A150" s="30" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B150" s="31">
         <v>1885</v>
@@ -12104,7 +12097,7 @@
     </row>
     <row r="151" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A151" s="24" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B151" s="25">
         <v>1886</v>
@@ -12179,7 +12172,7 @@
     </row>
     <row r="152" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A152" s="30" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B152" s="31">
         <v>1887</v>
@@ -12254,7 +12247,7 @@
     </row>
     <row r="153" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A153" s="24" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B153" s="25">
         <v>1888</v>
@@ -12329,7 +12322,7 @@
     </row>
     <row r="154" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A154" s="30" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B154" s="31">
         <v>1889</v>
@@ -12404,7 +12397,7 @@
     </row>
     <row r="155" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A155" s="24" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B155" s="25">
         <v>1890</v>
@@ -12479,7 +12472,7 @@
     </row>
     <row r="156" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A156" s="30" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B156" s="31">
         <v>1891</v>
@@ -12554,7 +12547,7 @@
     </row>
     <row r="157" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A157" s="24" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B157" s="25">
         <v>1892</v>
@@ -12629,7 +12622,7 @@
     </row>
     <row r="158" spans="1:23" x14ac:dyDescent="0.55000000000000004">
       <c r="A158" s="36" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B158" s="37">
         <v>1893</v>
